--- a/naver-place-crawler/results_health/강서구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/강서구_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Q2" t="n">
         <v>1778</v>
       </c>
       <c r="R2" t="n">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>랩스휘트니스 까치산점 헬스 PT</t>
+          <t>스토리짐 여성전용 헬스 가양점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rapsfit11@naver.com</t>
+          <t>urbanstorypt@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1484-6681</t>
+          <t>0507-1486-1627</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 27 8층</t>
+          <t>서울특별시 강서구 양천로 470 지하1층 101호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsfit11</t>
+          <t>https://blog.naver.com/urbanstorypt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>811</v>
+        <v>243</v>
       </c>
       <c r="Q3" t="n">
-        <v>1988</v>
+        <v>386</v>
       </c>
       <c r="R3" t="n">
-        <v>2799</v>
+        <v>629</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1579879801</t>
+          <t>1091230027</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579879801</t>
+          <t>https://m.place.naver.com/place/1091230027</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스토리짐 여성전용 헬스 가양점</t>
+          <t>스포애니 우장산역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>urbanstorypt@naver.com</t>
+          <t>spoany93@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1486-1627</t>
+          <t>0507-1308-8802</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 양천로 470 지하1층 101호</t>
+          <t>서울특별시 강서구 강서로 267 송화쇼핑센터 9층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/urbanstorypt</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>240</v>
+        <v>1072</v>
       </c>
       <c r="Q4" t="n">
-        <v>385</v>
+        <v>1567</v>
       </c>
       <c r="R4" t="n">
-        <v>625</v>
+        <v>2639</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1091230027</t>
+          <t>1893634711</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091230027</t>
+          <t>https://m.place.naver.com/place/1893634711</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 우장산역점</t>
+          <t>스포애니 가양역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany93@naver.com</t>
+          <t>spoany115@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1308-8802</t>
+          <t>0507-1458-9618</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 267 송화쇼핑센터 9층</t>
+          <t>서울특별시 강서구 양천로 510 B1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA4</t>
+          <t>https://www.instagram.com/spoany115/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1070</v>
+        <v>632</v>
       </c>
       <c r="Q5" t="n">
-        <v>1556</v>
+        <v>1671</v>
       </c>
       <c r="R5" t="n">
-        <v>2626</v>
+        <v>2303</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1893634711</t>
+          <t>1468247423</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1893634711</t>
+          <t>https://m.place.naver.com/place/1468247423</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 가양역점</t>
+          <t>바운드짐 화곡역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany115@naver.com</t>
+          <t>boundgym2104@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1458-9618</t>
+          <t>0507-1345-0834</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 양천로 510 B1층</t>
+          <t>서울특별시 강서구 강서로 173 터보빌딩 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spoany115/</t>
+          <t>https://link.inpock.co.kr/boundgym04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>631</v>
+        <v>2529</v>
       </c>
       <c r="Q6" t="n">
-        <v>1663</v>
+        <v>3764</v>
       </c>
       <c r="R6" t="n">
-        <v>2294</v>
+        <v>6293</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1468247423</t>
+          <t>1580860988</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468247423</t>
+          <t>https://m.place.naver.com/place/1580860988</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바운드짐 화곡역점</t>
+          <t>스포애니 화곡역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>boundgym2104@naver.com</t>
+          <t>spoany45@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1345-0834</t>
+          <t>0507-1428-9981</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 173 터보빌딩 6층</t>
+          <t>서울특별시 강서구 화곡로 191 남서울타워 B2, B1, 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/boundgym04</t>
+          <t>https://www.instagram.com/spoany45/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2526</v>
+        <v>2242</v>
       </c>
       <c r="Q7" t="n">
-        <v>3749</v>
+        <v>1628</v>
       </c>
       <c r="R7" t="n">
-        <v>6275</v>
+        <v>3870</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1580860988</t>
+          <t>1588177165</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1580860988</t>
+          <t>https://m.place.naver.com/place/1588177165</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>자마이카 휘트니스 화곡점</t>
+          <t>버핏그라운드 마곡 원그로브</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jamaicahwagok@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1309-9976</t>
+          <t>0507-1399-3624</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로 161 대성빌딩</t>
+          <t>서울특별시 강서구 공항대로 165 원그로브 C동 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jamaicahwagok</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1269</v>
+        <v>943</v>
       </c>
       <c r="Q8" t="n">
-        <v>1769</v>
+        <v>144</v>
       </c>
       <c r="R8" t="n">
-        <v>3038</v>
+        <v>1087</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>18394104</t>
+          <t>2038453115</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18394104</t>
+          <t>https://m.place.naver.com/place/2038453115</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1282,10 +1286,10 @@
         <v>442</v>
       </c>
       <c r="Q9" t="n">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="R9" t="n">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1304,7 +1308,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 화곡역점</t>
+          <t>휴메이크휘트니스 발산역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>humake08@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-2602-3912</t>
+          <t>0507-1438-0437</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
+          <t>서울특별시 강서구 강서로52길 43 B01호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/humake08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1309</v>
+        <v>1342</v>
       </c>
       <c r="Q10" t="n">
-        <v>1495</v>
+        <v>681</v>
       </c>
       <c r="R10" t="n">
-        <v>2804</v>
+        <v>2023</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1818807982</t>
+          <t>1771558329</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1818807982</t>
+          <t>https://m.place.naver.com/place/1771558329</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>나무 EMS스파&amp;운동 마곡점</t>
+          <t>휘트니스피플 우먼 화곡역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>goforit_20_@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-6080-2096</t>
+          <t>02-2602-3912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
+          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goforit_20_</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>77</v>
+        <v>1312</v>
       </c>
       <c r="Q11" t="n">
-        <v>223</v>
+        <v>1495</v>
       </c>
       <c r="R11" t="n">
-        <v>300</v>
+        <v>2807</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,51 +1486,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1611015705</t>
+          <t>1818807982</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611015705</t>
+          <t>https://m.place.naver.com/place/1818807982</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>바디채널 화곡2호점</t>
+          <t>운동으로우주정복PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bodygymmm@naver.com</t>
+          <t>unujeong2023@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1409-2606</t>
+          <t>0507-1341-9365</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 곰달래로 198 2층</t>
+          <t>서울특별시 강서구 마곡중앙로 161-8 에이동 2층 201,202호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodygymmm</t>
+          <t>https://blog.naver.com/unujeong2023</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1561,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="Q12" t="n">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="R12" t="n">
-        <v>372</v>
+        <v>417</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,111 +1580,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1348945802</t>
+          <t>1432557076</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1348945802</t>
+          <t>https://m.place.naver.com/place/1432557076</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>밸런스22짐 헬스&amp;PT 화곡점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>poha0092@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1389-0198</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>서울특별시 강서구 강서로 199 2층, 3층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/poha0092</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>426</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>641</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1067</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1208400007</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1208400007</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
